--- a/diseases/d094/2005-2009.xlsx
+++ b/diseases/d094/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>1098</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>20.92990540368984</v>
       </c>
@@ -1787,9 +1784,6 @@
       <c r="O7" t="n">
         <v>1589</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>34.37069825511927</v>
       </c>
@@ -2331,9 +2325,6 @@
       <c r="O10" t="n">
         <v>957</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>18.24218531086628</v>
       </c>
@@ -2966,9 +2957,6 @@
       <c r="O13" t="n">
         <v>1465</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>31.68852922828805</v>
       </c>
@@ -3510,9 +3498,6 @@
       <c r="O16" t="n">
         <v>985</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>18.775916960505</v>
       </c>
@@ -4145,9 +4130,6 @@
       <c r="O19" t="n">
         <v>1370</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>29.63364166740931</v>
       </c>
@@ -4689,9 +4671,6 @@
       <c r="O22" t="n">
         <v>1016</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>19.36683414403359</v>
       </c>
@@ -5324,9 +5303,6 @@
       <c r="O25" t="n">
         <v>1882</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>40.70840410077688</v>
       </c>
@@ -5868,9 +5844,6 @@
       <c r="O28" t="n">
         <v>1066</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>20.3199263755313</v>
       </c>
@@ -6503,9 +6476,6 @@
       <c r="O31" t="n">
         <v>1564</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>33.8299383706775</v>
       </c>
@@ -7047,9 +7017,6 @@
       <c r="O34" t="n">
         <v>948</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>18.07062870919669</v>
       </c>
@@ -7682,9 +7649,6 @@
       <c r="O37" t="n">
         <v>1798</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>38.89145088905251</v>
       </c>
@@ -8226,9 +8190,6 @@
       <c r="O40" t="n">
         <v>910</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>17.34627861325843</v>
       </c>
@@ -8861,9 +8822,6 @@
       <c r="O43" t="n">
         <v>1385</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>29.95809759807437</v>
       </c>
@@ -9405,9 +9363,6 @@
       <c r="O46" t="n">
         <v>1272</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>24.24666636930189</v>
       </c>
@@ -10040,9 +9995,6 @@
       <c r="O49" t="n">
         <v>1743</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>37.7017791432806</v>
       </c>
@@ -10584,9 +10536,6 @@
       <c r="O52" t="n">
         <v>1172</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>22.34048190630646</v>
       </c>
@@ -11219,9 +11168,6 @@
       <c r="O55" t="n">
         <v>2113</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>45.70502543301889</v>
       </c>
@@ -11763,9 +11709,6 @@
       <c r="O58" t="n">
         <v>1107</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>21.10146200535943</v>
       </c>
@@ -12398,9 +12341,6 @@
       <c r="O61" t="n">
         <v>1685</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>36.44721621137568</v>
       </c>
@@ -12942,9 +12882,6 @@
       <c r="O64" t="n">
         <v>1264</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>24.09417161226226</v>
       </c>
@@ -13577,9 +13514,6 @@
       <c r="O67" t="n">
         <v>1848</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>39.97297065793607</v>
       </c>
@@ -14121,9 +14055,6 @@
       <c r="O70" t="n">
         <v>951</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>18.12781424308655</v>
       </c>
@@ -14756,9 +14687,6 @@
       <c r="O73" t="n">
         <v>1521</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>32.89983136943763</v>
       </c>
@@ -15300,9 +15228,6 @@
       <c r="O76" t="n">
         <v>1226</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>23.28033828268388</v>
       </c>
@@ -16174,9 +16099,6 @@
       <c r="O80" t="n">
         <v>1761</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>37.78569396291466</v>
       </c>
@@ -16718,9 +16640,6 @@
       <c r="O83" t="n">
         <v>1089</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>20.67886491830567</v>
       </c>
@@ -17353,9 +17272,6 @@
       <c r="O86" t="n">
         <v>1696</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>36.39099202788374</v>
       </c>
@@ -17897,9 +17813,6 @@
       <c r="O89" t="n">
         <v>1238</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>23.5082045627754</v>
       </c>
@@ -18532,9 +18445,6 @@
       <c r="O92" t="n">
         <v>1908</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>40.93986603136921</v>
       </c>
@@ -19076,9 +18986,6 @@
       <c r="O95" t="n">
         <v>984</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>18.68503496750484</v>
       </c>
@@ -19711,9 +19618,6 @@
       <c r="O98" t="n">
         <v>1369</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>29.37456844703587</v>
       </c>
@@ -20255,9 +20159,6 @@
       <c r="O101" t="n">
         <v>1209</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>22.95752771922089</v>
       </c>
@@ -20890,9 +20791,6 @@
       <c r="O104" t="n">
         <v>1722</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>36.94887280189611</v>
       </c>
@@ -21434,9 +21332,6 @@
       <c r="O107" t="n">
         <v>1081</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>20.52695406491132</v>
       </c>
@@ -22069,9 +21964,6 @@
       <c r="O110" t="n">
         <v>1700</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>36.47681983927026</v>
       </c>
@@ -22613,9 +22505,6 @@
       <c r="O113" t="n">
         <v>979</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>18.59009068413338</v>
       </c>
@@ -23248,9 +23137,6 @@
       <c r="O116" t="n">
         <v>1375</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>29.50331016411565</v>
       </c>
@@ -23792,9 +23678,6 @@
       <c r="O119" t="n">
         <v>1444</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>27.41990903767988</v>
       </c>
@@ -24427,9 +24310,6 @@
       <c r="O122" t="n">
         <v>1889</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>40.53218392728324</v>
       </c>
@@ -24971,9 +24851,6 @@
       <c r="O125" t="n">
         <v>1285</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>24.4006808264672</v>
       </c>
@@ -25606,9 +25483,6 @@
       <c r="O128" t="n">
         <v>2150</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>46.13244862025356</v>
       </c>
@@ -26150,9 +26024,6 @@
       <c r="O131" t="n">
         <v>1214</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>23.05247200259236</v>
       </c>
@@ -26785,9 +26656,6 @@
       <c r="O134" t="n">
         <v>1990</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>42.69933616479283</v>
       </c>
@@ -27329,9 +27197,6 @@
       <c r="O137" t="n">
         <v>1189</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>22.57775058573502</v>
       </c>
@@ -27964,9 +27829,6 @@
       <c r="O140" t="n">
         <v>2057</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>44.13695200551701</v>
       </c>
@@ -28508,9 +28370,6 @@
       <c r="O143" t="n">
         <v>937</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>17.79255870381305</v>
       </c>
@@ -29143,9 +29002,6 @@
       <c r="O146" t="n">
         <v>1642</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>35.23231657416574</v>
       </c>
@@ -29687,9 +29543,6 @@
       <c r="O149" t="n">
         <v>1233</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>23.31381376554963</v>
       </c>
@@ -30561,9 +30414,6 @@
       <c r="O153" t="n">
         <v>2119</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>44.99884264420759</v>
       </c>
@@ -31105,9 +30955,6 @@
       <c r="O156" t="n">
         <v>1029</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>19.45654044180906</v>
       </c>
@@ -31740,9 +31587,6 @@
       <c r="O159" t="n">
         <v>1819</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>38.6280768144472</v>
       </c>
@@ -32284,9 +32128,6 @@
       <c r="O162" t="n">
         <v>1021</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>19.30527482127021</v>
       </c>
@@ -32919,9 +32760,6 @@
       <c r="O165" t="n">
         <v>1893</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>40.1995323857881</v>
       </c>
@@ -33463,9 +33301,6 @@
       <c r="O168" t="n">
         <v>1011</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>19.11619279559666</v>
       </c>
@@ -34098,9 +33933,6 @@
       <c r="O171" t="n">
         <v>1596</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>33.8924742143253</v>
       </c>
@@ -34642,9 +34474,6 @@
       <c r="O174" t="n">
         <v>1199</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>22.67093487825954</v>
       </c>
@@ -35277,9 +35106,6 @@
       <c r="O177" t="n">
         <v>1908</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>40.51807067727611</v>
       </c>
@@ -35821,9 +35647,6 @@
       <c r="O180" t="n">
         <v>1045</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>19.75907168288676</v>
       </c>
@@ -36456,9 +36279,6 @@
       <c r="O183" t="n">
         <v>1942</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>41.24009080464896</v>
       </c>
@@ -37000,9 +36820,6 @@
       <c r="O186" t="n">
         <v>1242</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>23.48398758865584</v>
       </c>
@@ -37635,9 +37452,6 @@
       <c r="O189" t="n">
         <v>1513</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>32.12989566809159</v>
       </c>
@@ -38179,9 +37993,6 @@
       <c r="O192" t="n">
         <v>1491</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>28.19213002792741</v>
       </c>
@@ -38814,9 +38625,6 @@
       <c r="O195" t="n">
         <v>1995</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>42.36559276790663</v>
       </c>
@@ -39358,9 +39166,6 @@
       <c r="O198" t="n">
         <v>1310</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>24.76974536323603</v>
       </c>
@@ -39993,9 +39798,6 @@
       <c r="O201" t="n">
         <v>2133</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>45.29614504959641</v>
       </c>
@@ -40537,9 +40339,6 @@
       <c r="O204" t="n">
         <v>1327</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>25.09118480688107</v>
       </c>
@@ -41172,9 +40971,6 @@
       <c r="O207" t="n">
         <v>2149</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>45.63591922718363</v>
       </c>
@@ -41716,9 +41512,6 @@
       <c r="O210" t="n">
         <v>1164</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>22.00914778840209</v>
       </c>
@@ -42351,9 +42144,6 @@
       <c r="O213" t="n">
         <v>2184</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>46.37917524065568</v>
       </c>
@@ -42895,9 +42685,6 @@
       <c r="O216" t="n">
         <v>891</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>16.84720848751397</v>
       </c>
@@ -43530,9 +43317,6 @@
       <c r="O219" t="n">
         <v>1596</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>33.8924742143253</v>
       </c>
@@ -44074,9 +43858,6 @@
       <c r="O222" t="n">
         <v>1380</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>25.97218303914817</v>
       </c>
@@ -44948,9 +44729,6 @@
       <c r="O226" t="n">
         <v>2208</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>46.30774390055915</v>
       </c>
@@ -45492,9 +45270,6 @@
       <c r="O229" t="n">
         <v>1168</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>21.98225347081527</v>
       </c>
@@ -46127,9 +45902,6 @@
       <c r="O232" t="n">
         <v>1941</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>40.70803030388828</v>
       </c>
@@ -46671,9 +46443,6 @@
       <c r="O235" t="n">
         <v>1024</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>19.27211263194763</v>
       </c>
@@ -47306,9 +47075,6 @@
       <c r="O238" t="n">
         <v>1576</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>33.05299111742809</v>
       </c>
@@ -47850,9 +47616,6 @@
       <c r="O241" t="n">
         <v>1210</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>22.77271121548499</v>
       </c>
@@ -48485,9 +48248,6 @@
       <c r="O244" t="n">
         <v>2181</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>45.7414807278621</v>
       </c>
@@ -49029,9 +48789,6 @@
       <c r="O247" t="n">
         <v>1127</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>21.21061614863768</v>
       </c>
@@ -49664,9 +49421,6 @@
       <c r="O250" t="n">
         <v>2022</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>42.40681982197944</v>
       </c>
@@ -50208,9 +49962,6 @@
       <c r="O253" t="n">
         <v>1022</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>19.23447178696335</v>
       </c>
@@ -50843,9 +50594,6 @@
       <c r="O256" t="n">
         <v>1826</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>38.29616864240082</v>
       </c>
@@ -51387,9 +51135,6 @@
       <c r="O259" t="n">
         <v>1049</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>19.74262319425104</v>
       </c>
@@ -52022,9 +51767,6 @@
       <c r="O262" t="n">
         <v>1556</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>32.63353691543028</v>
       </c>
@@ -52566,9 +52308,6 @@
       <c r="O265" t="n">
         <v>1253</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>23.58198938264686</v>
       </c>
@@ -53201,9 +52940,6 @@
       <c r="O268" t="n">
         <v>1938</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>40.6451121735886</v>
       </c>
@@ -53745,9 +53481,6 @@
       <c r="O271" t="n">
         <v>1302</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>24.50419008476154</v>
       </c>
@@ -54380,9 +54113,6 @@
       <c r="O274" t="n">
         <v>2499</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>52.4108025396274</v>
       </c>
@@ -54924,9 +54654,6 @@
       <c r="O277" t="n">
         <v>1273</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>23.95839783248958</v>
       </c>
@@ -55559,9 +55286,6 @@
       <c r="O280" t="n">
         <v>2232</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>46.81108894295654</v>
       </c>
@@ -56103,9 +55827,6 @@
       <c r="O283" t="n">
         <v>1055</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>19.85554572920386</v>
       </c>
@@ -56738,9 +56459,6 @@
       <c r="O286" t="n">
         <v>1833</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>38.44297761310006</v>
       </c>
@@ -57282,9 +57000,6 @@
       <c r="O289" t="n">
         <v>985</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>18.53811615475431</v>
       </c>
@@ -57917,9 +57632,6 @@
       <c r="O292" t="n">
         <v>1676</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>35.15026212741718</v>
       </c>
@@ -58461,9 +58173,6 @@
       <c r="O295" t="n">
         <v>1237</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>23.16975554596757</v>
       </c>
@@ -59335,9 +59044,6 @@
       <c r="O299" t="n">
         <v>2053</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>42.51730177705961</v>
       </c>
@@ -59879,9 +59585,6 @@
       <c r="O302" t="n">
         <v>1059</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>19.83570826449446</v>
       </c>
@@ -60514,9 +60217,6 @@
       <c r="O305" t="n">
         <v>1782</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>36.90493510312724</v>
       </c>
@@ -61058,9 +60758,6 @@
       <c r="O308" t="n">
         <v>1186</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>22.21449480801741</v>
       </c>
@@ -61693,9 +61390,6 @@
       <c r="O311" t="n">
         <v>2176</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>45.06461211246064</v>
       </c>
@@ -62237,9 +61931,6 @@
       <c r="O314" t="n">
         <v>1087</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>20.36016514023181</v>
       </c>
@@ -62872,9 +62563,6 @@
       <c r="O317" t="n">
         <v>1807</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>37.42268110625753</v>
       </c>
@@ -63416,9 +63104,6 @@
       <c r="O320" t="n">
         <v>1005</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>18.82425571842959</v>
       </c>
@@ -64051,9 +63736,6 @@
       <c r="O323" t="n">
         <v>1990</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>41.21258184917127</v>
       </c>
@@ -64595,9 +64277,6 @@
       <c r="O326" t="n">
         <v>1010</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>18.91790873195412</v>
       </c>
@@ -65230,9 +64909,6 @@
       <c r="O329" t="n">
         <v>1900</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>39.34869623790222</v>
       </c>
@@ -65774,9 +65450,6 @@
       <c r="O332" t="n">
         <v>1071</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>20.06047549695333</v>
       </c>
@@ -66409,9 +66082,6 @@
       <c r="O335" t="n">
         <v>1598</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>33.09432452008829</v>
       </c>
@@ -66953,9 +66623,6 @@
       <c r="O338" t="n">
         <v>1174</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>21.98972757555855</v>
       </c>
@@ -67588,9 +67255,6 @@
       <c r="O341" t="n">
         <v>1776</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>36.78067606237597</v>
       </c>
@@ -68132,9 +67796,6 @@
       <c r="O344" t="n">
         <v>1261</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>23.61929001088529</v>
       </c>
@@ -68767,9 +68428,6 @@
       <c r="O347" t="n">
         <v>2098</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>43.44924458269413</v>
       </c>
@@ -69311,9 +68969,6 @@
       <c r="O350" t="n">
         <v>1219</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>22.83260469727928</v>
       </c>
@@ -69946,9 +69601,6 @@
       <c r="O353" t="n">
         <v>1981</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>41.02619328804437</v>
       </c>
@@ -70490,9 +70142,6 @@
       <c r="O356" t="n">
         <v>996</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>18.65568029408545</v>
       </c>
@@ -71125,9 +70774,6 @@
       <c r="O359" t="n">
         <v>1812</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>37.52623030688359</v>
       </c>
@@ -71669,9 +71315,6 @@
       <c r="O362" t="n">
         <v>1006</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>18.8429863211345</v>
       </c>
@@ -72303,9 +71946,6 @@
       </c>
       <c r="O365" t="n">
         <v>1781</v>
-      </c>
-      <c r="Q365" t="n">
-        <v>0</v>
       </c>
       <c r="R365" t="n">
         <v>36.88422526300202</v>
